--- a/services_forms/005_morning_cleaning_checklist--services_forms.xlsx
+++ b/services_forms/005_morning_cleaning_checklist--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>morning_cleaning_checklist_page</t>
+          <t>morning_tasks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morning Cleaning Checklist</t>
+          <t>What are the tasks to be performed in the morning?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>daily_tasks</t>
+          <t>Is this task completed daily?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>Who is assigned to perform this task?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>What is the start time for this task?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>What is the end time for this task?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>What location is this task performed at?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Are there any notes for this task?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>What tool is assigned for this task?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>Who created this task?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>Who updated this task?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>When was this task created?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>When was this task updated?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>When was this task completed?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>completed_by</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>Who completed this task?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>assigned_to_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>Assigned To 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>tool_details</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>What details about the tool?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>task_status</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>What is the task status?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>Are there any additional notes?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1182,29 +1021,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_to_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>team_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Team A</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1055,148 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>tool_a</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Tool A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>assigned_tool_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tool_b</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tool B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>assigned_tool_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tool_c</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tool C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>assigned_to_2_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>john_doe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>John Doe</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>assigned_to_2_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>jane_doe</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Jane Doe</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>assigned_to_2_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>team_a</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>task_status_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>task_status_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>task_status_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
